--- a/prosecutors_data.xlsx
+++ b/prosecutors_data.xlsx
@@ -1,263 +1,204 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xueti\Desktop\检察官画像\app\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B58537-EAEC-40F8-AB42-4413B5722F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18540" yWindow="1680" windowWidth="36840" windowHeight="19350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12225"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="56">
   <si>
     <t>姓名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>部门</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>政治面貌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>身份</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>政治能力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>案件办理能力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>法律监督能力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>数字检察能力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>调查研究能力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>群众工作能力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>马艳君</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>一部</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>中共党员</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>检察官</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>陈莹璐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石林山</t>
   </si>
   <si>
     <t>周芹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>石林山</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>周岩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>龚洁婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张梦</t>
   </si>
   <si>
     <t>宋迎新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>张梦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>庄小茜</t>
+  </si>
+  <si>
+    <t>张瀚</t>
+  </si>
+  <si>
+    <t>群众</t>
   </si>
   <si>
     <t>赵越超</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>庄小茜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>张瀚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>群众</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>黄敏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>王瑞婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亓悦然</t>
   </si>
   <si>
     <t>王睿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亓悦然</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>郑俪丹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林晨</t>
+  </si>
+  <si>
+    <t>齐志杰</t>
   </si>
   <si>
     <t>周鹏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林晨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>齐志杰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘诗雨</t>
   </si>
   <si>
     <t>韩晔琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘诗雨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>周炜杰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>检察官助理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>张文心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵琨</t>
   </si>
   <si>
     <t>马鑫悦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>付倩倩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵琨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>陈敏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郭秋月</t>
+  </si>
+  <si>
+    <t>共青团员</t>
+  </si>
+  <si>
+    <t>卢菲</t>
   </si>
   <si>
     <t>王栖梧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>卢菲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄逸凡</t>
+  </si>
+  <si>
+    <t>王以敏</t>
+  </si>
+  <si>
+    <t>姬烁</t>
   </si>
   <si>
     <t>翟瑞峰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>郭秋月</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>共青团员</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄逸凡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张娴</t>
+  </si>
+  <si>
+    <t>丁凯泽</t>
+  </si>
+  <si>
+    <t>温雅妮</t>
   </si>
   <si>
     <t>高溢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王以敏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>姬烁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>丁凯泽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>温雅妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高逸飞</t>
   </si>
   <si>
     <t>石瑞鑫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>张娴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -266,20 +207,356 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -287,31 +564,317 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="5" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="5" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="6" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="8" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="7" applyNumberFormat="false" applyFont="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="1" builtinId="51"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="2" builtinId="50"/>
+    <cellStyle name="强调文字颜色 6" xfId="3" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="4" builtinId="47"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="5" builtinId="46"/>
+    <cellStyle name="强调文字颜色 5" xfId="6" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="7" builtinId="43"/>
+    <cellStyle name="标题 3" xfId="8" builtinId="18"/>
+    <cellStyle name="解释性文本" xfId="9" builtinId="53"/>
+    <cellStyle name="汇总" xfId="10" builtinId="25"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="千位分隔" xfId="12" builtinId="3"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="货币[0]" xfId="14" builtinId="7"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="15" builtinId="44"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="17" builtinId="34"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="18" builtinId="48"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="超链接" xfId="20" builtinId="8"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="21" builtinId="38"/>
+    <cellStyle name="货币" xfId="22" builtinId="4"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="23" builtinId="42"/>
+    <cellStyle name="计算" xfId="24" builtinId="22"/>
+    <cellStyle name="已访问的超链接" xfId="25" builtinId="9"/>
+    <cellStyle name="千位分隔[0]" xfId="26" builtinId="6"/>
+    <cellStyle name="强调文字颜色 4" xfId="27" builtinId="41"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="28" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="29" builtinId="52"/>
+    <cellStyle name="输入" xfId="30" builtinId="20"/>
+    <cellStyle name="输出" xfId="31" builtinId="21"/>
+    <cellStyle name="检查单元格" xfId="32" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="33" builtinId="24"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="34" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="35" builtinId="40"/>
+    <cellStyle name="注释" xfId="36" builtinId="10"/>
+    <cellStyle name="标题" xfId="37" builtinId="15"/>
+    <cellStyle name="好" xfId="38" builtinId="26"/>
+    <cellStyle name="标题 4" xfId="39" builtinId="19"/>
+    <cellStyle name="强调文字颜色 1" xfId="40" builtinId="29"/>
+    <cellStyle name="适中" xfId="41" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="42" builtinId="30"/>
+    <cellStyle name="差" xfId="43" builtinId="27"/>
+    <cellStyle name="强调文字颜色 2" xfId="44" builtinId="33"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="45" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="46" builtinId="36"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="47" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="48" builtinId="37"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -433,7 +996,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -454,9 +1017,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="16200000" scaled="true"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -477,7 +1040,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="16200000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -547,7 +1110,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -573,7 +1136,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -596,19 +1159,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J41"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="10" max="10" width="27.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.625" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="1" ht="15.75" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -640,7 +1203,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -654,25 +1217,25 @@
         <v>13</v>
       </c>
       <c r="E2" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="F2" s="3">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G2" s="3">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="H2" s="3">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="I2" s="3">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="J2" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -689,22 +1252,22 @@
         <v>6</v>
       </c>
       <c r="F3" s="3">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G3" s="3">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="H3" s="3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I3" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J3" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -718,25 +1281,25 @@
         <v>13</v>
       </c>
       <c r="E4" s="3">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="F4" s="3">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="G4" s="3">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="H4" s="3">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I4" s="3">
-        <v>6</v>
+        <v>8.7</v>
       </c>
       <c r="J4" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -750,25 +1313,25 @@
         <v>13</v>
       </c>
       <c r="E5" s="3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="F5" s="3">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="G5" s="3">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="H5" s="3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I5" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J5" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -782,25 +1345,25 @@
         <v>13</v>
       </c>
       <c r="E6" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="F6" s="3">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="G6" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I6" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J6" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -814,25 +1377,25 @@
         <v>13</v>
       </c>
       <c r="E7" s="3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="F7" s="3">
-        <v>6</v>
+        <v>8.9</v>
       </c>
       <c r="G7" s="3">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="H7" s="3">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="I7" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J7" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -846,25 +1409,25 @@
         <v>13</v>
       </c>
       <c r="E8" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="F8" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
       </c>
       <c r="H8" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I8" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J8" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -878,25 +1441,25 @@
         <v>13</v>
       </c>
       <c r="E9" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="F9" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9" s="3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H9" s="3">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I9" s="3">
         <v>6</v>
       </c>
       <c r="J9" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -910,25 +1473,25 @@
         <v>13</v>
       </c>
       <c r="E10" s="3">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="F10" s="3">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="G10" s="3">
-        <v>6</v>
+        <v>9.3</v>
       </c>
       <c r="H10" s="3">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I10" s="3">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="J10" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -936,39 +1499,39 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="F11" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H11" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I11" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J11" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -977,22 +1540,22 @@
         <v>6</v>
       </c>
       <c r="F12" s="3">
-        <v>6</v>
+        <v>8.3</v>
       </c>
       <c r="G12" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H12" s="3">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I12" s="3">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="J12" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1006,25 +1569,25 @@
         <v>13</v>
       </c>
       <c r="E13" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F13" s="3">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="G13" s="3">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H13" s="3">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I13" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J13" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1038,25 +1601,25 @@
         <v>13</v>
       </c>
       <c r="E14" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F14" s="3">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="G14" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H14" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I14" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J14" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1070,25 +1633,25 @@
         <v>13</v>
       </c>
       <c r="E15" s="3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="F15" s="3">
-        <v>6</v>
+        <v>8.2</v>
       </c>
       <c r="G15" s="3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H15" s="3">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I15" s="3">
         <v>6</v>
       </c>
       <c r="J15" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1102,25 +1665,25 @@
         <v>13</v>
       </c>
       <c r="E16" s="3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="F16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="3">
-        <v>6</v>
+        <v>9.3</v>
       </c>
       <c r="I16" s="3">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="J16" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1134,25 +1697,25 @@
         <v>13</v>
       </c>
       <c r="E17" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="F17" s="3">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="G17" s="3">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H17" s="3">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="I17" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J17" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -1166,25 +1729,25 @@
         <v>13</v>
       </c>
       <c r="E18" s="3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="F18" s="3">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G18" s="3">
-        <v>6</v>
+        <v>8.2</v>
       </c>
       <c r="H18" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I18" s="3">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J18" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -1198,25 +1761,25 @@
         <v>13</v>
       </c>
       <c r="E19" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F19" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G19" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I19" s="3">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J19" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -1230,25 +1793,25 @@
         <v>13</v>
       </c>
       <c r="E20" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="F20" s="3">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="G20" s="3">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="H20" s="3">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I20" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J20" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -1262,25 +1825,25 @@
         <v>13</v>
       </c>
       <c r="E21" s="3">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="F21" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G21" s="3">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="H21" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I21" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J21" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -1312,7 +1875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -1326,25 +1889,25 @@
         <v>36</v>
       </c>
       <c r="E23" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="F23" s="3">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="G23" s="3">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="H23" s="3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I23" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J23" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -1358,25 +1921,25 @@
         <v>36</v>
       </c>
       <c r="E24" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F24" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G24" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H24" s="3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I24" s="3">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="J24" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1390,25 +1953,25 @@
         <v>36</v>
       </c>
       <c r="E25" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="F25" s="3">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="G25" s="3">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="H25" s="3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I25" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J25" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -1422,25 +1985,25 @@
         <v>36</v>
       </c>
       <c r="E26" s="3">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="F26" s="3">
-        <v>6</v>
+        <v>8.3</v>
       </c>
       <c r="G26" s="3">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H26" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I26" s="3">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="J26" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+        <v>9.3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1454,25 +2017,25 @@
         <v>36</v>
       </c>
       <c r="E27" s="3">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="F27" s="3">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="G27" s="3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H27" s="3">
         <v>6</v>
       </c>
       <c r="I27" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -1486,25 +2049,25 @@
         <v>36</v>
       </c>
       <c r="E28" s="3">
-        <v>6</v>
+        <v>8.2</v>
       </c>
       <c r="F28" s="3">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G28" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H28" s="3">
         <v>6</v>
       </c>
       <c r="I28" s="3">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="J28" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -1512,33 +2075,33 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
         <v>36</v>
       </c>
       <c r="E29" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="F29" s="3">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="G29" s="3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H29" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I29" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J29" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
@@ -1550,27 +2113,27 @@
         <v>36</v>
       </c>
       <c r="E30" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="F30" s="3">
-        <v>6</v>
+        <v>8.8</v>
       </c>
       <c r="G30" s="3">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="H30" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I30" s="3">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J30" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
@@ -1582,57 +2145,57 @@
         <v>36</v>
       </c>
       <c r="E31" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="F31" s="3">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="G31" s="3">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="H31" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I31" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J31" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
         <v>36</v>
       </c>
       <c r="E32" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="F32" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G32" s="3">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="H32" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I32" s="3">
         <v>6</v>
       </c>
       <c r="J32" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -1640,31 +2203,31 @@
         <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="D33" t="s">
         <v>36</v>
       </c>
       <c r="E33" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F33" s="3">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G33" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H33" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I33" s="3">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J33" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -1672,31 +2235,31 @@
         <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="D34" t="s">
         <v>36</v>
       </c>
       <c r="E34" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="F34" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G34" s="3">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="H34" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I34" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J34" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -1704,31 +2267,31 @@
         <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
         <v>36</v>
       </c>
       <c r="E35" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="F35" s="3">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="G35" s="3">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="H35" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I35" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J35" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -1736,31 +2299,31 @@
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
         <v>36</v>
       </c>
       <c r="E36" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="F36" s="3">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="G36" s="3">
-        <v>6</v>
+        <v>8.2</v>
       </c>
       <c r="H36" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I36" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J36" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -1774,25 +2337,25 @@
         <v>36</v>
       </c>
       <c r="E37" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="F37" s="3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="G37" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H37" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I37" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J37" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>52</v>
       </c>
@@ -1806,25 +2369,25 @@
         <v>36</v>
       </c>
       <c r="E38" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="F38" s="3">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="G38" s="3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H38" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I38" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J38" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>53</v>
       </c>
@@ -1832,31 +2395,31 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D39" t="s">
         <v>36</v>
       </c>
       <c r="E39" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="F39" s="3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="G39" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H39" s="3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I39" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J39" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>54</v>
       </c>
@@ -1870,26 +2433,58 @@
         <v>36</v>
       </c>
       <c r="E40" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="F40" s="3">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="G40" s="3">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="H40" s="3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I40" s="3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J40" s="3">
-        <v>6</v>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41">
+        <v>5.6</v>
+      </c>
+      <c r="F41">
+        <v>6.8</v>
+      </c>
+      <c r="G41">
+        <v>5.6</v>
+      </c>
+      <c r="H41">
+        <v>5.8</v>
+      </c>
+      <c r="I41">
+        <v>5.9</v>
+      </c>
+      <c r="J41">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/prosecutors_data.xlsx
+++ b/prosecutors_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xueti\Desktop\检察官画像\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E21EAD-67A8-49AE-A827-B0792E8AE2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C9BF9C-FBD5-4A83-8F4B-7F77E607A4F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6420" yWindow="4425" windowWidth="39105" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26895" yWindow="2520" windowWidth="24720" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="117">
   <si>
     <t>姓名</t>
   </si>
@@ -137,9 +137,6 @@
   </si>
   <si>
     <t>赵琨</t>
-  </si>
-  <si>
-    <t>马鑫悦</t>
   </si>
   <si>
     <t>付倩倩</t>
@@ -374,6 +371,15 @@
   </si>
   <si>
     <t>参与部门系列涉外活动；参与部门涉侨工作</t>
+  </si>
+  <si>
+    <t>2015.10</t>
+  </si>
+  <si>
+    <t>参与涉性侵案件工作、诉判不一致调研等</t>
+  </si>
+  <si>
+    <t>参与部门涉毒品案件工作</t>
   </si>
 </sst>
 </file>
@@ -381,7 +387,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -433,14 +439,14 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -743,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="6" width="9" style="2"/>
@@ -770,19 +776,19 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>4</v>
@@ -823,13 +829,13 @@
         <v>2009.7</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="J2" s="6">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="K2" s="6">
         <v>6.5</v>
@@ -841,7 +847,7 @@
         <v>8.4</v>
       </c>
       <c r="N2" s="6">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="O2" s="6">
         <v>7.8</v>
@@ -867,13 +873,13 @@
         <v>2016.7</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="J3" s="6">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="K3" s="6">
         <v>7.5</v>
@@ -885,7 +891,7 @@
         <v>6.2</v>
       </c>
       <c r="N3" s="6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O3" s="6">
         <v>6.7</v>
@@ -911,13 +917,13 @@
         <v>2012.7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J4" s="6">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="K4" s="6">
         <v>6.7</v>
@@ -929,7 +935,7 @@
         <v>5.2</v>
       </c>
       <c r="N4" s="6">
-        <v>8.6999999999999993</v>
+        <v>7.9</v>
       </c>
       <c r="O4" s="6">
         <v>6.5</v>
@@ -955,10 +961,10 @@
         <v>2010.7</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="J5" s="6">
         <v>5.8</v>
@@ -999,13 +1005,13 @@
         <v>2002.7</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="J6" s="6">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="K6" s="6">
         <v>7.4</v>
@@ -1043,16 +1049,16 @@
         <v>2008.8</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="J7" s="6">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="K7" s="6">
         <v>8.9</v>
@@ -1090,13 +1096,13 @@
         <v>2015.7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J8" s="6">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="K8" s="6">
         <v>7</v>
@@ -1134,10 +1140,10 @@
         <v>2004.8</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J9" s="6">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="K9" s="6">
         <v>8</v>
@@ -1171,17 +1177,17 @@
       <c r="E10" s="2">
         <v>1990.4</v>
       </c>
-      <c r="F10" s="2">
-        <v>2015.1</v>
+      <c r="F10" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J10" s="6">
-        <v>6.3</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="K10" s="6">
         <v>6.9</v>
@@ -1193,7 +1199,7 @@
         <v>5.2</v>
       </c>
       <c r="N10" s="6">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="O10" s="6">
         <v>8</v>
@@ -1219,16 +1225,16 @@
         <v>2007.7</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="J11" s="6">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="K11" s="6">
         <v>7</v>
@@ -1266,13 +1272,13 @@
         <v>2008.7</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J12" s="6">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K12" s="6">
         <v>8.3000000000000007</v>
@@ -1284,7 +1290,7 @@
         <v>5.5</v>
       </c>
       <c r="N12" s="6">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="O12" s="6">
         <v>6.4</v>
@@ -1310,16 +1316,16 @@
         <v>2012.8</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="J13" s="6">
-        <v>5.9</v>
+        <v>8.5</v>
       </c>
       <c r="K13" s="6">
         <v>7.6</v>
@@ -1357,13 +1363,13 @@
         <v>2014.9</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J14" s="6">
-        <v>5.9</v>
+        <v>8.5</v>
       </c>
       <c r="K14" s="6">
         <v>7.1</v>
@@ -1398,16 +1404,16 @@
         <v>1992.3</v>
       </c>
       <c r="F15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="J15" s="6">
-        <v>5.8</v>
+        <v>8.9</v>
       </c>
       <c r="K15" s="6">
         <v>8.1999999999999993</v>
@@ -1442,16 +1448,16 @@
         <v>1991.1</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="J16" s="6">
-        <v>5.8</v>
+        <v>8.9</v>
       </c>
       <c r="K16" s="6">
         <v>7</v>
@@ -1463,7 +1469,7 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="N16" s="6">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="O16" s="6">
         <v>6.8</v>
@@ -1486,19 +1492,19 @@
         <v>1989.1</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="J17" s="6">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="K17" s="6">
         <v>6.7</v>
@@ -1533,13 +1539,13 @@
         <v>1993.1</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="J18" s="6">
-        <v>5.8</v>
+        <v>8.5</v>
       </c>
       <c r="K18" s="6">
         <v>7.5</v>
@@ -1551,7 +1557,7 @@
         <v>5</v>
       </c>
       <c r="N18" s="6">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="O18" s="6">
         <v>6.4</v>
@@ -1574,19 +1580,19 @@
         <v>1989.11</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="J19" s="6">
-        <v>5.9</v>
+        <v>8.5</v>
       </c>
       <c r="K19" s="6">
         <v>8</v>
@@ -1598,7 +1604,7 @@
         <v>5</v>
       </c>
       <c r="N19" s="6">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="O19" s="6">
         <v>6.4</v>
@@ -1621,16 +1627,16 @@
         <v>1990.8</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="J20" s="6">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="K20" s="6">
         <v>6.7</v>
@@ -1665,16 +1671,16 @@
         <v>1995.1</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="J21" s="6">
-        <v>8.1</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="K21" s="6">
         <v>7</v>
@@ -1686,7 +1692,7 @@
         <v>5.7</v>
       </c>
       <c r="N21" s="6">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
       <c r="O21" s="6">
         <v>6.4</v>
@@ -1705,11 +1711,17 @@
       <c r="D22" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="E22" s="2">
+        <v>1991.3</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2016.7</v>
+      </c>
       <c r="J22" s="6">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="K22" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L22" s="6">
         <v>6</v>
@@ -1721,7 +1733,7 @@
         <v>6</v>
       </c>
       <c r="O22" s="6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.15">
@@ -1744,16 +1756,16 @@
         <v>2017.7</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="J23" s="6">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="K23" s="6">
         <v>6.8</v>
@@ -1765,7 +1777,7 @@
         <v>5.8</v>
       </c>
       <c r="N23" s="6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O23" s="6">
         <v>6.5</v>
@@ -1791,10 +1803,10 @@
         <v>2020.1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J24" s="6">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="K24" s="6">
         <v>8</v>
@@ -1806,7 +1818,7 @@
         <v>6.2</v>
       </c>
       <c r="N24" s="6">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="O24" s="6">
         <v>6.9</v>
@@ -1832,13 +1844,13 @@
         <v>2021.7</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="J25" s="6">
-        <v>5.6</v>
+        <v>8.5</v>
       </c>
       <c r="K25" s="6">
         <v>7.1</v>
@@ -1850,7 +1862,7 @@
         <v>6.2</v>
       </c>
       <c r="N25" s="6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O25" s="6">
         <v>6.7</v>
@@ -1870,34 +1882,37 @@
         <v>36</v>
       </c>
       <c r="E26" s="2">
-        <v>1997.8</v>
+        <v>1997.11</v>
       </c>
       <c r="F26" s="2">
         <v>2021.7</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>77</v>
+        <v>100</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="J26" s="6">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="K26" s="6">
-        <v>8.3000000000000007</v>
+        <v>6.9</v>
       </c>
       <c r="L26" s="6">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="M26" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N26" s="6">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="O26" s="6">
-        <v>9.3000000000000007</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.15">
@@ -1914,37 +1929,37 @@
         <v>36</v>
       </c>
       <c r="E27" s="2">
-        <v>1997.11</v>
+        <v>1996.11</v>
       </c>
       <c r="F27" s="2">
         <v>2021.7</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>102</v>
       </c>
       <c r="J27" s="6">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="K27" s="6">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="L27" s="6">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="M27" s="6">
         <v>6</v>
       </c>
       <c r="N27" s="6">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="O27" s="6">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
@@ -1955,87 +1970,84 @@
         <v>11</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="2">
-        <v>1996.11</v>
+      <c r="E28" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="F28" s="2">
-        <v>2021.7</v>
+        <v>2023.7</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J28" s="6">
-        <v>8.1999999999999993</v>
+        <v>8.4</v>
       </c>
       <c r="K28" s="6">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="L28" s="6">
+        <v>5.8</v>
+      </c>
+      <c r="M28" s="6">
         <v>5.6</v>
       </c>
-      <c r="M28" s="6">
-        <v>6</v>
-      </c>
       <c r="N28" s="6">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="O28" s="6">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F29" s="2">
         <v>2023.7</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>105</v>
       </c>
       <c r="J29" s="6">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="K29" s="6">
-        <v>7.4</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="L29" s="6">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="M29" s="6">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="N29" s="6">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="O29" s="6">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
@@ -2051,35 +2063,35 @@
       <c r="D30" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>104</v>
+      <c r="E30" s="2">
+        <v>1998.4</v>
       </c>
       <c r="F30" s="2">
-        <v>2023.7</v>
+        <v>2022.7</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>106</v>
       </c>
       <c r="J30" s="6">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="K30" s="6">
-        <v>8.8000000000000007</v>
+        <v>6.8</v>
       </c>
       <c r="L30" s="6">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="M30" s="6">
         <v>5.7</v>
       </c>
       <c r="N30" s="6">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O30" s="6">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.15">
@@ -2095,32 +2107,32 @@
       <c r="D31" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="2">
-        <v>1998.4</v>
+      <c r="E31" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="F31" s="2">
-        <v>2022.7</v>
+        <v>2024.7</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J31" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="K31" s="6">
+        <v>8</v>
+      </c>
+      <c r="L31" s="6">
+        <v>7.3</v>
+      </c>
+      <c r="M31" s="6">
         <v>5.6</v>
       </c>
-      <c r="K31" s="6">
-        <v>6.8</v>
-      </c>
-      <c r="L31" s="6">
-        <v>6.9</v>
-      </c>
-      <c r="M31" s="6">
-        <v>5.7</v>
-      </c>
       <c r="N31" s="6">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="O31" s="6">
         <v>6.6</v>
@@ -2134,40 +2146,37 @@
         <v>11</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>108</v>
+      <c r="E32" s="2">
+        <v>2000.9</v>
       </c>
       <c r="F32" s="2">
         <v>2024.7</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="J32" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="K32" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="L32" s="6">
+        <v>5.9</v>
+      </c>
+      <c r="M32" s="6">
         <v>5.7</v>
       </c>
-      <c r="K32" s="6">
-        <v>8</v>
-      </c>
-      <c r="L32" s="6">
-        <v>7.3</v>
-      </c>
-      <c r="M32" s="6">
-        <v>5.6</v>
-      </c>
       <c r="N32" s="6">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="O32" s="6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.15">
@@ -2178,37 +2187,40 @@
         <v>11</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E33" s="2">
-        <v>2000.9</v>
+        <v>1998.12</v>
       </c>
       <c r="F33" s="2">
         <v>2024.7</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="J33" s="6">
+        <v>8.4</v>
+      </c>
+      <c r="K33" s="6">
+        <v>7</v>
+      </c>
+      <c r="L33" s="6">
+        <v>6.3</v>
+      </c>
+      <c r="M33" s="6">
+        <v>5.6</v>
+      </c>
+      <c r="N33" s="6">
         <v>5.9</v>
       </c>
-      <c r="K33" s="6">
-        <v>7.5</v>
-      </c>
-      <c r="L33" s="6">
-        <v>5.9</v>
-      </c>
-      <c r="M33" s="6">
-        <v>5.7</v>
-      </c>
-      <c r="N33" s="6">
-        <v>6.1</v>
-      </c>
       <c r="O33" s="6">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
@@ -2219,37 +2231,37 @@
         <v>11</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E34" s="2">
-        <v>1998.12</v>
+        <v>1998.2</v>
       </c>
       <c r="F34" s="2">
         <v>2024.7</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>110</v>
       </c>
       <c r="J34" s="6">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="K34" s="6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L34" s="6">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="M34" s="6">
         <v>5.6</v>
       </c>
       <c r="N34" s="6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O34" s="6">
         <v>6.5</v>
@@ -2269,31 +2281,31 @@
         <v>36</v>
       </c>
       <c r="E35" s="2">
-        <v>1998.2</v>
+        <v>1999.8</v>
       </c>
       <c r="F35" s="2">
         <v>2024.7</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J35" s="6">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="K35" s="6">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L35" s="6">
-        <v>5.4</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="M35" s="6">
         <v>5.6</v>
       </c>
       <c r="N35" s="6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O35" s="6">
         <v>6.5</v>
@@ -2313,34 +2325,34 @@
         <v>36</v>
       </c>
       <c r="E36" s="2">
-        <v>1999.8</v>
+        <v>1998.5</v>
       </c>
       <c r="F36" s="2">
-        <v>2024.7</v>
+        <v>2025.7</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>112</v>
       </c>
       <c r="J36" s="6">
+        <v>8.4</v>
+      </c>
+      <c r="K36" s="6">
+        <v>6.6</v>
+      </c>
+      <c r="L36" s="6">
         <v>5.6</v>
-      </c>
-      <c r="K36" s="6">
-        <v>6.8</v>
-      </c>
-      <c r="L36" s="6">
-        <v>8.1999999999999993</v>
       </c>
       <c r="M36" s="6">
         <v>5.6</v>
       </c>
       <c r="N36" s="6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O36" s="6">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
@@ -2357,34 +2369,34 @@
         <v>36</v>
       </c>
       <c r="E37" s="2">
-        <v>1998.5</v>
+        <v>2000.4</v>
       </c>
       <c r="F37" s="2">
         <v>2025.7</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>113</v>
       </c>
       <c r="J37" s="6">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="K37" s="6">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="L37" s="6">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="M37" s="6">
         <v>5.6</v>
       </c>
       <c r="N37" s="6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O37" s="6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
@@ -2401,34 +2413,34 @@
         <v>36</v>
       </c>
       <c r="E38" s="2">
-        <v>2000.4</v>
+        <v>2001.6</v>
       </c>
       <c r="F38" s="2">
         <v>2025.7</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="J38" s="6">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="K38" s="6">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="L38" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="M38" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="N38" s="6">
         <v>5.8</v>
       </c>
-      <c r="M38" s="6">
-        <v>5.6</v>
-      </c>
-      <c r="N38" s="6">
-        <v>5.9</v>
-      </c>
       <c r="O38" s="6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
@@ -2445,34 +2457,34 @@
         <v>36</v>
       </c>
       <c r="E39" s="2">
-        <v>2001.6</v>
+        <v>2000.11</v>
       </c>
       <c r="F39" s="2">
         <v>2025.7</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="J39" s="6">
+        <v>8.4</v>
+      </c>
+      <c r="K39" s="6">
+        <v>7.2</v>
+      </c>
+      <c r="L39" s="6">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="M39" s="6">
         <v>5.6</v>
       </c>
-      <c r="K39" s="6">
-        <v>6.6</v>
-      </c>
-      <c r="L39" s="6">
-        <v>5.7</v>
-      </c>
-      <c r="M39" s="6">
-        <v>5.7</v>
-      </c>
       <c r="N39" s="6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O39" s="6">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.15">
@@ -2483,77 +2495,39 @@
         <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E40" s="2">
-        <v>2000.11</v>
+        <v>1998.3</v>
       </c>
       <c r="F40" s="2">
         <v>2025.7</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="J40" s="6">
+        <v>8.4</v>
+      </c>
+      <c r="K40" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="L40" s="6">
         <v>5.6</v>
       </c>
-      <c r="K40" s="6">
-        <v>7.2</v>
-      </c>
-      <c r="L40" s="6">
-        <v>4.9000000000000004</v>
-      </c>
       <c r="M40" s="6">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="N40" s="6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O40" s="6">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A41" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E41" s="2">
-        <v>1998.3</v>
-      </c>
-      <c r="F41" s="2">
-        <v>2025.7</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J41" s="7">
-        <v>5.6</v>
-      </c>
-      <c r="K41" s="7">
-        <v>6.8</v>
-      </c>
-      <c r="L41" s="7">
-        <v>5.6</v>
-      </c>
-      <c r="M41" s="7">
-        <v>5.8</v>
-      </c>
-      <c r="N41" s="7">
-        <v>5.9</v>
-      </c>
-      <c r="O41" s="7">
         <v>6.5</v>
       </c>
     </row>
